--- a/catalog/evidence/normal-chat-t05-final.xlsx
+++ b/catalog/evidence/normal-chat-t05-final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuuki\ai-prompts\catalog\evidence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F567E48D-0AAD-46F7-8014-06E0D854D212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A56E4A9D-BE7E-4D56-B621-0A6FB0AEA562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{F6C7D14D-0971-4AB2-8FFC-8F2855D3F312}"/>
   </bookViews>
